--- a/www/terminologies/CodeSystem-TRE-R85-RolePriseCharge.xlsx
+++ b/www/terminologies/CodeSystem-TRE-R85-RolePriseCharge.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="242">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260202120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-02-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>74</t>
+    <t>75</t>
   </si>
   <si>
     <t>Code</t>
@@ -731,6 +731,15 @@
   </si>
   <si>
     <t>Technicien d’études cliniques</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Agent d'autorité d'enregistrement</t>
+  </si>
+  <si>
+    <t>Les agents des autorités d’enregistrement sont des personnes habilitées à collecter, vérifier et transmettre les données d’identification des professionnels de santé vers les systèmes officiels, notamment le RPPS et le tableau si l’autorité d’enregistrement est un Ordre médical. Ils jouent un rôle crucial dans la gestion administrative et réglementaire de la profession. L’agent d’enregistrement vérifie les diplômes, les pièces justificatives et les conditions d’exercice du professionnel. Pour une profession ordinale, il ou elle enregistre le professionnel dans le tableau officiel de l’Ordre et lui attribue un numéro ordinal. Les données validées (identité, spécialité, lieu d’exercice, etc.) sont quotidiennement transmises au RPPS. Elles sont considérées comme fiables et opposables, car elles proviennent d’autorités officielles que sont les Ordres professionnels, les ARS ou le Service de santé des armées.</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2111,6 +2120,20 @@
       </c>
       <c r="D75" s="2"/>
     </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="C76" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="D76" t="s" s="2">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/terminologies/CodeSystem-TRE-R85-RolePriseCharge.xlsx
+++ b/www/terminologies/CodeSystem-TRE-R85-RolePriseCharge.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="245">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260202120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>75</t>
+    <t>76</t>
   </si>
   <si>
     <t>Code</t>
@@ -740,6 +740,15 @@
   </si>
   <si>
     <t>Les agents des autorités d’enregistrement sont des personnes habilitées à collecter, vérifier et transmettre les données d’identification des professionnels de santé vers les systèmes officiels, notamment le RPPS et le tableau si l’autorité d’enregistrement est un Ordre médical. Ils jouent un rôle crucial dans la gestion administrative et réglementaire de la profession. L’agent d’enregistrement vérifie les diplômes, les pièces justificatives et les conditions d’exercice du professionnel. Pour une profession ordinale, il ou elle enregistre le professionnel dans le tableau officiel de l’Ordre et lui attribue un numéro ordinal. Les données validées (identité, spécialité, lieu d’exercice, etc.) sont quotidiennement transmises au RPPS. Elles sont considérées comme fiables et opposables, car elles proviennent d’autorités officielles que sont les Ordres professionnels, les ARS ou le Service de santé des armées.</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Conseiller conjugal et familial</t>
+  </si>
+  <si>
+    <t>Ref juridique : arrêté du 3 décembre 2010 relatif à la formation des personnels intervenant dans les centres de planification ou d’éducation familiale et dans les établissements d’information, de consultation ou de conseil familial.​ Le Conseiller conjugal et familial exerce – auprès des jeunes, des femmes, des couples et des familles – des activités d’information, d’orientation et d’accompagnement dans tous les domaines liés à la vie affective et sexuelle, aux conduites à risques, aux discriminations, aux violences (sexuelles, sexistes, de couple...), aux problèmes relationnels dans le couple et dans la famille. ​ Il s’inscrit dans le cadre de la promotion de la santé et de l’approche globale des personnes en matière d’éducation à la sexualité. Il s’appuie sur l’analyse de pratique, la formation continue, le travail en réseau et le cadre déontologique de l'écoute active pour répondre au plus juste aux besoins des personnes.</t>
   </si>
 </sst>
 </file>
@@ -1155,7 +1164,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2134,6 +2143,20 @@
         <v>241</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/terminologies/CodeSystem-TRE-R85-RolePriseCharge.xlsx
+++ b/www/terminologies/CodeSystem-TRE-R85-RolePriseCharge.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="257">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>76</t>
+    <t>80</t>
   </si>
   <si>
     <t>Code</t>
@@ -322,7 +322,7 @@
     <t>317</t>
   </si>
   <si>
-    <t>Préparateur en pharmacie (officine)</t>
+    <t>Préparateur en pharmacie</t>
   </si>
   <si>
     <t>Ref juridique : CSP Articles L4241-1 à L4241-18 Source fiche métier de la Fédération des Pharmaciens d’Officine (FPO) : https://www.fspf.fr/wp-content/uploads/2024/01/Fiche-metier-et-formation-Preparateur-en-pharmacie.pdf Le préparateur en pharmacie est un professionnel de santé qui exerce sous la responsabilité du pharmacien, il accueille les clients, délivre les médicaments et peut être amené à passer les commandes et gérer les stocks pour l’officine. Ses rôles d’accueil et de conseil sont également très importants.</t>
@@ -749,6 +749,42 @@
   </si>
   <si>
     <t>Ref juridique : arrêté du 3 décembre 2010 relatif à la formation des personnels intervenant dans les centres de planification ou d’éducation familiale et dans les établissements d’information, de consultation ou de conseil familial.​ Le Conseiller conjugal et familial exerce – auprès des jeunes, des femmes, des couples et des familles – des activités d’information, d’orientation et d’accompagnement dans tous les domaines liés à la vie affective et sexuelle, aux conduites à risques, aux discriminations, aux violences (sexuelles, sexistes, de couple...), aux problèmes relationnels dans le couple et dans la famille. ​ Il s’inscrit dans le cadre de la promotion de la santé et de l’approche globale des personnes en matière d’éducation à la sexualité. Il s’appuie sur l’analyse de pratique, la formation continue, le travail en réseau et le cadre déontologique de l'écoute active pour répondre au plus juste aux besoins des personnes.</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>PADHUE - Médecin</t>
+  </si>
+  <si>
+    <t>Médecin formé à l’étranger (hors UE) qui travaille dans le système de santé français avant ou pendant la procédure de reconnaissance de son diplôme étranger afin d’obtenir une autorisation de plein exercice. Le diplôme de ce professionnel n'est pas enregistré au RPPS avant l'obtention de l'autorisation de plein exercice, le justificatif sera alors enregistré par l'Ordre.</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>PADHUE - Pharmacien</t>
+  </si>
+  <si>
+    <t>Pharmacien formé à l’étranger (hors UE) qui travaille dans le système de santé français avant ou pendant la procédure de reconnaissance de son diplôme étranger afin d’obtenir une autorisation de plein exercice. Le diplôme de ce professionnel n'est pas enregistré au RPPS avant l'obtention de l'autorisation de plein exercice, le justificatif sera alors enregistré par l'Ordre.</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>PADHUE - Sage Femme</t>
+  </si>
+  <si>
+    <t>Sage Femme formé à l’étranger (hors UE) qui travaille dans le système de santé français avant ou pendant la procédure de reconnaissance de son diplôme étranger afin d’obtenir une autorisation de plein exercice. Le diplôme de ce professionnel n'est pas enregistré au RPPS avant l'obtention de l'autorisation de plein exercice, le justificatif sera alors enregistré par l'Ordre.</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>PADHUE - Chirurgien Dentiste</t>
+  </si>
+  <si>
+    <t>Chirurgien Dentiste formé à l’étranger (hors UE) qui travaille dans le système de santé français avant ou pendant la procédure de reconnaissance de son diplôme étranger afin d’obtenir une autorisation de plein exercice. Le diplôme de ce professionnel n'est pas enregistré au RPPS avant l'obtention de l'autorisation de plein exercice, le justificatif sera alors enregistré par l'Ordre.</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2157,6 +2193,62 @@
         <v>244</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="D78" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="D79" t="s" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="D80" t="s" s="2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="D81" t="s" s="2">
+        <v>256</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
